--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportReviewTg001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportReviewTg001.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Reaton\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67438D58-ECE5-4F60-AAF8-BE613864BE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E704D0F0-D717-4DCC-BE75-2C32BFD34844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
-    <t>复核时间</t>
-  </si>
-  <si>
     <t>复核人</t>
   </si>
   <si>
@@ -75,6 +72,10 @@
   </si>
   <si>
     <t>托管复核人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>报表复核时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -423,52 +424,52 @@
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
